--- a/performance-dashboard/archive/交易表现_20260311.xlsx
+++ b/performance-dashboard/archive/交易表现_20260311.xlsx
@@ -533,26 +533,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>¥1,003,008.57</t>
+          <t>¥1,013,310.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>¥+3,008.57</t>
+          <t>¥+13,310.87</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+0.30%</t>
+          <t>+1.33%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+4.30%</t>
+          <t>+19.17%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.374</v>
+        <v>2.107</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -561,24 +561,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.0187%</t>
+          <t>0.0748%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>7.3180%</t>
+          <t>8.0015%</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -587,7 +587,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -609,26 +609,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>¥1,018,121.62</t>
+          <t>¥1,027,056.98</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>¥+18,121.62</t>
+          <t>¥+27,056.98</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+1.81%</t>
+          <t>+2.71%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+28.59%</t>
+          <t>+42.49%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.948</v>
+        <v>2.784</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -637,24 +637,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.1091%</t>
+          <t>0.1518%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>13.0934%</t>
+          <t>13.0278%</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -663,7 +663,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -685,26 +685,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>¥1,003,192.72</t>
+          <t>¥1,017,795.74</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>¥+3,192.72</t>
+          <t>¥+17,795.74</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>+1.78%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+4.56%</t>
+          <t>+26.36%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.661</v>
+        <v>3.432</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -713,24 +713,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.0191%</t>
+          <t>0.0989%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>4.2952%</t>
+          <t>6.6866%</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -761,26 +761,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>¥1,009,825.68</t>
+          <t>¥1,012,616.68</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>¥+9,825.68</t>
+          <t>¥+12,616.68</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+0.98%</t>
+          <t>+1.26%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+14.67%</t>
+          <t>+18.09%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2.312</v>
+        <v>2.92</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -789,24 +789,24 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.0581%</t>
+          <t>0.0703%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>5.4799%</t>
+          <t>5.3843%</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -837,26 +837,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>¥988,498.15</t>
+          <t>¥990,085.88</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>¥-11,501.85</t>
+          <t>¥-9,914.12</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-1.15%</t>
+          <t>-0.99%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-14.95%</t>
+          <t>-12.38%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>-2.138</v>
+        <v>-1.818</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -865,24 +865,24 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>-0.0665%</t>
+          <t>-0.0539%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>8.7655%</t>
+          <t>8.5585%</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -913,26 +913,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>¥1,015,332.99</t>
+          <t>¥1,017,331.69</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>¥+15,332.99</t>
+          <t>¥+17,331.69</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+1.53%</t>
+          <t>+1.73%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+23.74%</t>
+          <t>+25.60%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>3.857</v>
+        <v>4.243</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -941,24 +941,24 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.0901%</t>
+          <t>0.0961%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>5.3750%</t>
+          <t>5.2380%</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -989,26 +989,26 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>¥1,025,690.35</t>
+          <t>¥1,025,292.99</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>¥+25,690.35</t>
+          <t>¥+25,292.99</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+2.57%</t>
+          <t>+2.53%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+42.64%</t>
+          <t>+39.28%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5.108</v>
+        <v>4.845</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1017,24 +1017,24 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.1503%</t>
+          <t>0.1398%</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>7.0265%</t>
+          <t>6.8630%</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -1065,26 +1065,26 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>¥1,024,543.77</t>
+          <t>¥1,029,419.77</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>¥+24,543.77</t>
+          <t>¥+29,419.77</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+2.45%</t>
+          <t>+2.94%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+40.42%</t>
+          <t>+46.90%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>3.908</v>
+        <v>4.52</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1093,24 +1093,24 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.1443%</t>
+          <t>0.1627%</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>8.7960%</t>
+          <t>8.6328%</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -1141,26 +1141,26 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>¥1,025,844.39</t>
+          <t>¥1,032,583.39</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>¥+25,844.39</t>
+          <t>¥+32,583.39</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+2.58%</t>
+          <t>+3.26%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+42.94%</t>
+          <t>+53.00%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>6.584</v>
+        <v>7.662</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1169,24 +1169,24 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.1508%</t>
+          <t>0.1789%</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>5.4707%</t>
+          <t>5.6261%</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -1217,26 +1217,26 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>¥1,029,984.76</t>
+          <t>¥1,033,468.02</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>¥+29,984.76</t>
+          <t>¥+33,468.02</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+3.00%</t>
+          <t>+3.35%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+51.23%</t>
+          <t>+54.75%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>4.225</v>
+        <v>4.572</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1245,24 +1245,24 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.1759%</t>
+          <t>0.1849%</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>10.0247%</t>
+          <t>9.7602%</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -1293,26 +1293,26 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>¥1,004,255.66</t>
+          <t>¥1,011,153.45</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>¥+4,255.66</t>
+          <t>¥+11,153.45</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>+1.12%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+6.13%</t>
+          <t>+15.85%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.605</v>
+        <v>1.782</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1321,24 +1321,24 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.0261%</t>
+          <t>0.0628%</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>7.6106%</t>
+          <t>7.7766%</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -1369,26 +1369,26 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>¥1,001,879.24</t>
+          <t>¥1,012,150.64</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>¥+1,879.24</t>
+          <t>¥+12,150.64</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>+1.22%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+2.66%</t>
+          <t>+17.37%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.131</v>
+        <v>1.523</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1397,24 +1397,24 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0.0129%</t>
+          <t>0.0692%</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>9.7295%</t>
+          <t>10.1466%</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -1445,26 +1445,26 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>¥1,008,533.49</t>
+          <t>¥1,017,234.07</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>¥+8,533.49</t>
+          <t>¥+17,234.07</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+0.85%</t>
+          <t>+1.72%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+12.63%</t>
+          <t>+25.44%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1.431</v>
+        <v>2.793</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1473,24 +1473,24 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.0512%</t>
+          <t>0.0962%</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>7.6233%</t>
+          <t>7.9746%</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -1521,12 +1521,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>¥999,273.30</t>
+          <t>¥999,306.30</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>¥-726.70</t>
+          <t>¥-693.70</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1536,11 +1536,11 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-1.01%</t>
+          <t>-0.92%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>-11.13</v>
+        <v>-10.997</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1549,24 +1549,24 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>-0.0043%</t>
+          <t>-0.0039%</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0.2747%</t>
+          <t>0.2684%</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -1597,26 +1597,26 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>¥999,412.03</t>
+          <t>¥999,786.03</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>¥-587.97</t>
+          <t>¥-213.97</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-0.82%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>-2.72</v>
+        <v>-2.213</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1625,24 +1625,24 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>-0.0034%</t>
+          <t>-0.0012%</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1.0467%</t>
+          <t>1.0280%</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -1673,26 +1673,26 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>¥979,208.46</t>
+          <t>¥992,699.32</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>¥-20,791.54</t>
+          <t>¥-7,300.68</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-2.08%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-25.48%</t>
+          <t>-9.26%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>-2.841</v>
+        <v>-0.927</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1701,24 +1701,24 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>-0.1209%</t>
+          <t>-0.0377%</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>11.4230%</t>
+          <t>12.3666%</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>¥1,008,890.44</t>
+          <t>¥1,010,094.44</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>¥+8,890.44</t>
+          <t>¥+10,094.44</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+0.89%</t>
+          <t>+1.01%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+13.19%</t>
+          <t>+14.25%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1.869</v>
+        <v>2.08</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1777,24 +1777,24 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0.0528%</t>
+          <t>0.0565%</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>6.0600%</t>
+          <t>5.8942%</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -1825,26 +1825,26 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>¥1,006,861.48</t>
+          <t>¥1,008,315.28</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>¥+6,861.48</t>
+          <t>¥+8,315.28</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>+0.83%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+10.05%</t>
+          <t>+11.61%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1.55</v>
+        <v>1.868</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1853,24 +1853,24 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.0408%</t>
+          <t>0.0466%</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>5.3576%</t>
+          <t>5.2202%</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -1901,26 +1901,26 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>¥1,007,817.21</t>
+          <t>¥1,009,244.51</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>¥+7,817.21</t>
+          <t>¥+9,244.51</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+0.78%</t>
+          <t>+0.92%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+11.52%</t>
+          <t>+12.98%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1.634</v>
+        <v>1.908</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1929,24 +1929,24 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.0465%</t>
+          <t>0.0518%</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>5.9626%</t>
+          <t>5.8050%</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -1977,26 +1977,26 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>¥1,025,245.55</t>
+          <t>¥1,030,200.75</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>¥+25,245.55</t>
+          <t>¥+30,200.75</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+2.52%</t>
+          <t>+3.02%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+41.77%</t>
+          <t>+48.38%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>6.364</v>
+        <v>7.239</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2005,24 +2005,24 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.1474%</t>
+          <t>0.1660%</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>5.5247%</t>
+          <t>5.5063%</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -2053,26 +2053,26 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>¥1,029,043.50</t>
+          <t>¥1,030,515.20</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>¥+29,043.50</t>
+          <t>¥+30,515.20</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+2.90%</t>
+          <t>+3.05%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+49.30%</t>
+          <t>+48.99%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>3.657</v>
+        <v>3.727</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2081,24 +2081,24 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.1710%</t>
+          <t>0.1695%</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>11.2452%</t>
+          <t>10.9288%</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -2225,26 +2225,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>¥1,003,008.57</t>
+          <t>¥1,013,310.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>¥+3,008.57</t>
+          <t>¥+13,310.87</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+0.30%</t>
+          <t>+1.33%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+4.30%</t>
+          <t>+19.17%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.374</v>
+        <v>2.107</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -2253,24 +2253,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.0187%</t>
+          <t>0.0748%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>7.3180%</t>
+          <t>8.0015%</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -2301,26 +2301,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>¥1,018,121.62</t>
+          <t>¥1,027,056.98</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>¥+18,121.62</t>
+          <t>¥+27,056.98</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+1.81%</t>
+          <t>+2.71%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+28.59%</t>
+          <t>+42.49%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.948</v>
+        <v>2.784</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -2329,24 +2329,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.1091%</t>
+          <t>0.1518%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>13.0934%</t>
+          <t>13.0278%</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -2377,26 +2377,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>¥1,003,192.72</t>
+          <t>¥1,017,795.74</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>¥+3,192.72</t>
+          <t>¥+17,795.74</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>+1.78%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+4.56%</t>
+          <t>+26.36%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.661</v>
+        <v>3.432</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -2405,24 +2405,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.0191%</t>
+          <t>0.0989%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>4.2952%</t>
+          <t>6.6866%</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -2453,26 +2453,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>¥1,009,825.68</t>
+          <t>¥1,012,616.68</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>¥+9,825.68</t>
+          <t>¥+12,616.68</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+0.98%</t>
+          <t>+1.26%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+14.67%</t>
+          <t>+18.09%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2.312</v>
+        <v>2.92</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -2481,24 +2481,24 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.0581%</t>
+          <t>0.0703%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>5.4799%</t>
+          <t>5.3843%</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -2529,26 +2529,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>¥988,498.15</t>
+          <t>¥990,085.88</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>¥-11,501.85</t>
+          <t>¥-9,914.12</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-1.15%</t>
+          <t>-0.99%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-14.95%</t>
+          <t>-12.38%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>-2.138</v>
+        <v>-1.818</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -2557,24 +2557,24 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>-0.0665%</t>
+          <t>-0.0539%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>8.7655%</t>
+          <t>8.5585%</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -2701,26 +2701,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>¥1,015,332.99</t>
+          <t>¥1,017,331.69</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>¥+15,332.99</t>
+          <t>¥+17,331.69</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+1.53%</t>
+          <t>+1.73%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+23.74%</t>
+          <t>+25.60%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>3.857</v>
+        <v>4.243</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -2729,24 +2729,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.0901%</t>
+          <t>0.0961%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>5.3750%</t>
+          <t>5.2380%</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -2777,26 +2777,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>¥1,025,690.35</t>
+          <t>¥1,025,292.99</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>¥+25,690.35</t>
+          <t>¥+25,292.99</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+2.57%</t>
+          <t>+2.53%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+42.64%</t>
+          <t>+39.28%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5.108</v>
+        <v>4.845</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -2805,24 +2805,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.1503%</t>
+          <t>0.1398%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>7.0265%</t>
+          <t>6.8630%</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -2853,26 +2853,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>¥1,024,543.77</t>
+          <t>¥1,029,419.77</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>¥+24,543.77</t>
+          <t>¥+29,419.77</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+2.45%</t>
+          <t>+2.94%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+40.42%</t>
+          <t>+46.90%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3.908</v>
+        <v>4.52</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -2881,24 +2881,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.1443%</t>
+          <t>0.1627%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>8.7960%</t>
+          <t>8.6328%</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -2929,26 +2929,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>¥1,025,844.39</t>
+          <t>¥1,032,583.39</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>¥+25,844.39</t>
+          <t>¥+32,583.39</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+2.58%</t>
+          <t>+3.26%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+42.94%</t>
+          <t>+53.00%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>6.584</v>
+        <v>7.662</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -2957,24 +2957,24 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.1508%</t>
+          <t>0.1789%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>5.4707%</t>
+          <t>5.6261%</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -3005,26 +3005,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>¥1,029,984.76</t>
+          <t>¥1,033,468.02</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>¥+29,984.76</t>
+          <t>¥+33,468.02</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+3.00%</t>
+          <t>+3.35%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+51.23%</t>
+          <t>+54.75%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>4.225</v>
+        <v>4.572</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -3033,24 +3033,24 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.1759%</t>
+          <t>0.1849%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>10.0247%</t>
+          <t>9.7602%</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -3177,26 +3177,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>¥1,004,255.66</t>
+          <t>¥1,011,153.45</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>¥+4,255.66</t>
+          <t>¥+11,153.45</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>+1.12%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+6.13%</t>
+          <t>+15.85%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.605</v>
+        <v>1.782</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -3205,24 +3205,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.0261%</t>
+          <t>0.0628%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>7.6106%</t>
+          <t>7.7766%</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -3253,26 +3253,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>¥1,001,879.24</t>
+          <t>¥1,012,150.64</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>¥+1,879.24</t>
+          <t>¥+12,150.64</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>+1.22%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+2.66%</t>
+          <t>+17.37%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.131</v>
+        <v>1.523</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -3281,24 +3281,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.0129%</t>
+          <t>0.0692%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>9.7295%</t>
+          <t>10.1466%</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -3329,26 +3329,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>¥1,008,533.49</t>
+          <t>¥1,017,234.07</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>¥+8,533.49</t>
+          <t>¥+17,234.07</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+0.85%</t>
+          <t>+1.72%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+12.63%</t>
+          <t>+25.44%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.431</v>
+        <v>2.793</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -3357,24 +3357,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.0512%</t>
+          <t>0.0962%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>7.6233%</t>
+          <t>7.9746%</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -3405,12 +3405,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>¥999,273.30</t>
+          <t>¥999,306.30</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>¥-726.70</t>
+          <t>¥-693.70</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -3420,11 +3420,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-1.01%</t>
+          <t>-0.92%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-11.13</v>
+        <v>-10.997</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -3433,24 +3433,24 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-0.0043%</t>
+          <t>-0.0039%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.2747%</t>
+          <t>0.2684%</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -3459,7 +3459,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -3481,26 +3481,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>¥999,412.03</t>
+          <t>¥999,786.03</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>¥-587.97</t>
+          <t>¥-213.97</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-0.82%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>-2.72</v>
+        <v>-2.213</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -3509,24 +3509,24 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>-0.0034%</t>
+          <t>-0.0012%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1.0467%</t>
+          <t>1.0280%</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -3653,26 +3653,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>¥979,208.46</t>
+          <t>¥992,699.32</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>¥-20,791.54</t>
+          <t>¥-7,300.68</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-2.08%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-25.48%</t>
+          <t>-9.26%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>-2.841</v>
+        <v>-0.927</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -3681,24 +3681,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-0.1209%</t>
+          <t>-0.0377%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>11.4230%</t>
+          <t>12.3666%</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -3825,26 +3825,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>¥1,008,890.44</t>
+          <t>¥1,010,094.44</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>¥+8,890.44</t>
+          <t>¥+10,094.44</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+0.89%</t>
+          <t>+1.01%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+13.19%</t>
+          <t>+14.25%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.869</v>
+        <v>2.08</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -3853,24 +3853,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.0528%</t>
+          <t>0.0565%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>6.0600%</t>
+          <t>5.8942%</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -3901,26 +3901,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>¥1,006,861.48</t>
+          <t>¥1,008,315.28</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>¥+6,861.48</t>
+          <t>¥+8,315.28</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>+0.83%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+10.05%</t>
+          <t>+11.61%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.55</v>
+        <v>1.868</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -3929,24 +3929,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.0408%</t>
+          <t>0.0466%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>5.3576%</t>
+          <t>5.2202%</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -3977,26 +3977,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>¥1,007,817.21</t>
+          <t>¥1,009,244.51</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>¥+7,817.21</t>
+          <t>¥+9,244.51</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+0.78%</t>
+          <t>+0.92%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+11.52%</t>
+          <t>+12.98%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.634</v>
+        <v>1.908</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -4005,24 +4005,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.0465%</t>
+          <t>0.0518%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>5.9626%</t>
+          <t>5.8050%</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -4053,26 +4053,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>¥1,025,245.55</t>
+          <t>¥1,030,200.75</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>¥+25,245.55</t>
+          <t>¥+30,200.75</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+2.52%</t>
+          <t>+3.02%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+41.77%</t>
+          <t>+48.38%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>6.364</v>
+        <v>7.239</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -4081,24 +4081,24 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.1474%</t>
+          <t>0.1660%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>5.5247%</t>
+          <t>5.5063%</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
@@ -4129,26 +4129,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>¥1,029,043.50</t>
+          <t>¥1,030,515.20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>¥+29,043.50</t>
+          <t>¥+30,515.20</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+2.90%</t>
+          <t>+3.05%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+49.30%</t>
+          <t>+48.99%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>3.657</v>
+        <v>3.727</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -4157,24 +4157,24 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.1710%</t>
+          <t>0.1695%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>11.2452%</t>
+          <t>10.9288%</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>20260310</t>
+          <t>20260311</t>
         </is>
       </c>
     </row>
